--- a/public/TagLuyenCoc.xlsx
+++ b/public/TagLuyenCoc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E445D90-0150-4B9C-B9F7-FC9EAB7215EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82D1083-0B6E-45CD-BC9D-2BE4A20BC8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="9" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="CDQ1" sheetId="23" r:id="rId1"/>
@@ -1949,18 +1949,6 @@
     <t>LB_W</t>
   </si>
   <si>
-    <t>TE_14601A</t>
-  </si>
-  <si>
-    <t>TE_14601B</t>
-  </si>
-  <si>
-    <t>TE_14602</t>
-  </si>
-  <si>
-    <t>PT_14602</t>
-  </si>
-  <si>
     <t>BY_S201AI01_7_I</t>
   </si>
   <si>
@@ -2148,6 +2136,18 @@
   </si>
   <si>
     <t>CDQ2_LB2</t>
+  </si>
+  <si>
+    <t>TE_14601</t>
+  </si>
+  <si>
+    <t>TE_14603</t>
+  </si>
+  <si>
+    <t>TE_14604</t>
+  </si>
+  <si>
+    <t>PT_14603</t>
   </si>
 </sst>
 </file>
@@ -2399,14 +2399,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>406</v>
@@ -3394,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>405</v>
@@ -3409,7 +3409,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>411</v>
@@ -3424,7 +3424,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>411</v>
@@ -3439,7 +3439,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>404</v>
@@ -3454,7 +3454,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>404</v>
@@ -3469,7 +3469,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>404</v>
@@ -3484,7 +3484,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>404</v>
@@ -3499,7 +3499,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>404</v>
@@ -3514,7 +3514,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>404</v>
@@ -3529,7 +3529,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>404</v>
@@ -3537,17 +3537,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4816,10 +4816,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4831,10 +4831,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4846,10 +4846,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4861,10 +4861,10 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -4876,10 +4876,10 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="18"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4891,10 +4891,10 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
@@ -4938,10 +4938,10 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
@@ -4953,10 +4953,10 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="18"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
@@ -4968,10 +4968,10 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="18"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
@@ -4983,10 +4983,10 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="18"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
@@ -4998,10 +4998,10 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
@@ -5013,10 +5013,10 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="18"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
@@ -5028,10 +5028,10 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="18"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
@@ -5043,10 +5043,10 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="18"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
@@ -5058,10 +5058,10 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="18"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
@@ -5073,10 +5073,10 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="18"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
@@ -5089,11 +5089,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -5106,6 +5101,11 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5120,93 +5120,94 @@
     <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>533</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>471</v>
+        <v>534</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>472</v>
+        <v>535</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>473</v>
+        <v>536</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="18"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>413</v>
@@ -5223,7 +5224,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>124</v>
@@ -5238,157 +5239,157 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="18"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="18"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="18"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="18"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="18"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="18"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="18"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="18"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>404</v>
@@ -5396,11 +5397,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -5413,6 +5409,11 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5439,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>411</v>
@@ -5454,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>411</v>
@@ -5469,7 +5470,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>404</v>
@@ -5484,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>404</v>
@@ -5499,7 +5500,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>404</v>
@@ -5514,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>404</v>
@@ -5529,7 +5530,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>404</v>
@@ -5544,7 +5545,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>404</v>
@@ -5559,7 +5560,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>404</v>
@@ -5589,7 +5590,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>410</v>
@@ -5604,7 +5605,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>404</v>
@@ -5619,7 +5620,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>406</v>
@@ -5634,7 +5635,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>406</v>
@@ -5670,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>411</v>
@@ -5685,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>411</v>
@@ -5700,7 +5701,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>404</v>
@@ -5715,7 +5716,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>404</v>
@@ -5730,7 +5731,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>404</v>
@@ -5745,7 +5746,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>404</v>
@@ -5760,7 +5761,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>404</v>
@@ -5775,7 +5776,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>404</v>
@@ -5790,7 +5791,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>404</v>
@@ -5820,7 +5821,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>410</v>
@@ -5837,7 +5838,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>404</v>
@@ -5852,7 +5853,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>406</v>
@@ -5867,7 +5868,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>406</v>
@@ -5903,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>411</v>
@@ -5918,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>411</v>
@@ -5933,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>404</v>
@@ -5948,7 +5949,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>404</v>
@@ -5963,7 +5964,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>404</v>
@@ -5978,7 +5979,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>404</v>
@@ -5993,7 +5994,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>404</v>
@@ -6008,7 +6009,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>404</v>
@@ -6023,7 +6024,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>404</v>
@@ -6053,7 +6054,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>410</v>
@@ -6070,7 +6071,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>404</v>
@@ -6085,7 +6086,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>406</v>
@@ -6100,7 +6101,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>406</v>

--- a/public/TagLuyenCoc.xlsx
+++ b/public/TagLuyenCoc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82D1083-0B6E-45CD-BC9D-2BE4A20BC8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D552AA-B1DD-41CA-A7B5-6436238CE9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
   </bookViews>
   <sheets>
     <sheet name="CDQ1" sheetId="23" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="536">
   <si>
     <t>Tag0</t>
   </si>
@@ -262,9 +262,6 @@
   </si>
   <si>
     <t>Đầu vào lò CDQ P5 PRA_14108（KPa）</t>
-  </si>
-  <si>
-    <t>Van đóng kín xoay vòng P7 PISA_14102（MPa）</t>
   </si>
   <si>
     <t>Chênh áp P6-P2  (Kpa)</t>
@@ -877,19 +874,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Van đóng kín xoay vòng P7 PISA_14102（MPa）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
     <t>Nhiệt độ trước bộ giảm nhiệt A (°C)</t>
   </si>
   <si>
@@ -2148,6 +2132,9 @@
   </si>
   <si>
     <t>PT_14603</t>
+  </si>
+  <si>
+    <t>Van đóng kín xoay vòng P7 PISA_14102（KPa）</t>
   </si>
 </sst>
 </file>
@@ -2755,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2770,10 +2757,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2785,10 +2772,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2800,10 +2787,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2815,10 +2802,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2830,10 +2817,10 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2845,10 +2832,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2862,10 +2849,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2877,10 +2864,10 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2892,10 +2879,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2907,10 +2894,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2922,10 +2909,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2937,10 +2924,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2952,10 +2939,10 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2967,10 +2954,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2982,10 +2969,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2997,10 +2984,10 @@
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3012,10 +2999,10 @@
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3027,10 +3014,10 @@
         <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3042,10 +3029,10 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3057,10 +3044,10 @@
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3072,10 +3059,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3087,10 +3074,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3102,10 +3089,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3119,10 +3106,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3134,10 +3121,10 @@
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3149,10 +3136,10 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3164,10 +3151,10 @@
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3181,10 +3168,10 @@
         <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3196,10 +3183,10 @@
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3211,10 +3198,10 @@
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3226,10 +3213,10 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3241,10 +3228,10 @@
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3256,97 +3243,97 @@
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="11"/>
       <c r="B35" s="1" t="s">
-        <v>73</v>
+        <v>535</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="11"/>
       <c r="B36" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="11"/>
       <c r="B37" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="11"/>
       <c r="B38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="12"/>
       <c r="B39" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -3372,167 +3359,167 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="23" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="23" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B6" s="23"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B7" s="23"/>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B10" s="23"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -3567,106 +3554,106 @@
         <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="11"/>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18.75">
       <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18.75">
       <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18.75">
       <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="11"/>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18.75">
       <c r="A7" s="12"/>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75">
@@ -3674,31 +3661,31 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="14"/>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="31.5">
@@ -3710,10 +3697,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="31.5">
@@ -3725,25 +3712,25 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="14"/>
       <c r="B12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="31.5">
@@ -3755,25 +3742,25 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="14"/>
       <c r="B14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="31.5">
@@ -3785,10 +3772,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="31.5">
@@ -3800,10 +3787,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75">
@@ -3815,25 +3802,25 @@
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="14"/>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="31.5">
@@ -3845,10 +3832,10 @@
         <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="31.5">
@@ -3860,10 +3847,10 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="31.5">
@@ -3875,10 +3862,10 @@
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75">
@@ -3890,10 +3877,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75">
@@ -3905,10 +3892,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75">
@@ -3920,10 +3907,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18.75">
@@ -3931,31 +3918,31 @@
         <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18.75">
       <c r="A26" s="11"/>
       <c r="B26" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75">
@@ -3967,25 +3954,25 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18.75">
       <c r="A28" s="12"/>
       <c r="B28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75">
@@ -3999,10 +3986,10 @@
         <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75">
@@ -4014,10 +4001,10 @@
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75">
@@ -4029,25 +4016,25 @@
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75">
       <c r="A32" s="11"/>
       <c r="B32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75">
@@ -4059,10 +4046,10 @@
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75">
@@ -4074,97 +4061,97 @@
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="11"/>
       <c r="B35" s="2" t="s">
-        <v>73</v>
+        <v>535</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="11"/>
       <c r="B36" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="11"/>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75">
       <c r="A38" s="11"/>
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="12"/>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="1"/>
       <c r="B40" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -4193,106 +4180,106 @@
         <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="11"/>
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18.75">
       <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18.75">
       <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18.75">
       <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="11"/>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18.75">
       <c r="A7" s="12"/>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75">
@@ -4300,31 +4287,31 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="14"/>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="31.5">
@@ -4336,10 +4323,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="31.5">
@@ -4351,25 +4338,25 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31.5">
       <c r="A12" s="14"/>
       <c r="B12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="31.5">
@@ -4381,25 +4368,25 @@
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="14"/>
       <c r="B14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="31.5">
@@ -4411,10 +4398,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="31.5">
@@ -4426,10 +4413,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75">
@@ -4441,25 +4428,25 @@
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75">
       <c r="A18" s="14"/>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="31.5">
@@ -4471,10 +4458,10 @@
         <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="31.5">
@@ -4486,10 +4473,10 @@
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75">
@@ -4501,10 +4488,10 @@
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75">
@@ -4516,10 +4503,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75">
@@ -4531,10 +4518,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75">
@@ -4546,10 +4533,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18.75">
@@ -4557,61 +4544,61 @@
         <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18.75">
       <c r="A26" s="11"/>
       <c r="B26" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>439</v>
+      <c r="D26" t="s">
+        <v>436</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75">
       <c r="A27" s="11"/>
       <c r="B27" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18.75">
       <c r="A28" s="12"/>
       <c r="B28" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75">
@@ -4619,178 +4606,178 @@
         <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="11"/>
       <c r="B30" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75">
       <c r="A31" s="11"/>
       <c r="B31" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75">
       <c r="A32" s="11"/>
       <c r="B32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="11"/>
       <c r="B33" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75">
       <c r="A34" s="11"/>
       <c r="B34" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="11"/>
       <c r="B35" s="2" t="s">
-        <v>116</v>
+        <v>535</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="11"/>
       <c r="B36" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="11"/>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75">
       <c r="A38" s="11"/>
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="12"/>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="1"/>
       <c r="B40" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -4817,274 +4804,274 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12"/>
       <c r="B8" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -5125,274 +5112,274 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12"/>
       <c r="B8" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -5431,214 +5418,214 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="14"/>
       <c r="B2" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="14"/>
       <c r="B4" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="14"/>
       <c r="B5" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="14"/>
       <c r="B6" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="14"/>
       <c r="B7" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="14"/>
       <c r="B8" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="14"/>
       <c r="B9" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="14"/>
       <c r="B10" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="15"/>
       <c r="B11" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
       <c r="A13" s="14"/>
       <c r="B13" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
       <c r="A14" s="15"/>
       <c r="B14" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5662,216 +5649,216 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="19"/>
       <c r="B2" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
       <c r="A3" s="19"/>
       <c r="B3" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="19"/>
       <c r="B4" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="19"/>
       <c r="B5" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="19"/>
       <c r="B6" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="19"/>
       <c r="B7" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="19"/>
       <c r="B8" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="19"/>
       <c r="B9" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="19"/>
       <c r="B10" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="19"/>
       <c r="B11" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
       <c r="A14" s="19"/>
       <c r="B14" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5895,216 +5882,216 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="19"/>
       <c r="B2" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1">
       <c r="A3" s="19"/>
       <c r="B3" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
       <c r="A4" s="19"/>
       <c r="B4" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
       <c r="A5" s="19"/>
       <c r="B5" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
       <c r="A6" s="19"/>
       <c r="B6" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
       <c r="A7" s="19"/>
       <c r="B7" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
       <c r="A8" s="19"/>
       <c r="B8" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
       <c r="A9" s="19"/>
       <c r="B9" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
       <c r="A10" s="19"/>
       <c r="B10" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
       <c r="A11" s="19"/>
       <c r="B11" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
       <c r="A12" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
       <c r="A14" s="19"/>
       <c r="B14" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -6128,1370 +6115,1370 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5">
       <c r="A1" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5">
       <c r="A2" s="21"/>
       <c r="B2" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5">
       <c r="A3" s="21"/>
       <c r="B3" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5">
       <c r="A4" s="21"/>
       <c r="B4" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5">
       <c r="A5" s="21"/>
       <c r="B5" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5">
       <c r="A6" s="21"/>
       <c r="B6" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5">
       <c r="A7" s="21"/>
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="21"/>
       <c r="B8" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="21"/>
       <c r="B9" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="21"/>
       <c r="B10" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="21"/>
       <c r="B12" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="21"/>
       <c r="B13" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="21"/>
       <c r="B14" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="21"/>
       <c r="B15" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.5">
       <c r="A16" s="21"/>
       <c r="B16" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16.5">
       <c r="A17" s="21"/>
       <c r="B17" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.5">
       <c r="A18" s="21"/>
       <c r="B18" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16.5">
       <c r="A19" s="21"/>
       <c r="B19" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16.5">
       <c r="A20" s="21"/>
       <c r="B20" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16.5">
       <c r="A21" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="21"/>
       <c r="B22" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16.5">
       <c r="A23" s="21"/>
       <c r="B23" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16.5">
       <c r="A24" s="21"/>
       <c r="B24" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5">
       <c r="A25" s="21"/>
       <c r="B25" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16.5">
       <c r="A26" s="21"/>
       <c r="B26" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16.5">
       <c r="A27" s="21"/>
       <c r="B27" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16.5">
       <c r="A28" s="21"/>
       <c r="B28" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16.5">
       <c r="A29" s="21"/>
       <c r="B29" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16.5">
       <c r="A30" s="21"/>
       <c r="B30" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5">
       <c r="A31" s="20" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="21"/>
       <c r="B32" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.5">
       <c r="A33" s="21"/>
       <c r="B33" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5">
       <c r="A34" s="21"/>
       <c r="B34" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5">
       <c r="A35" s="21"/>
       <c r="B35" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5">
       <c r="A36" s="21"/>
       <c r="B36" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.5">
       <c r="A37" s="21"/>
       <c r="B37" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5">
       <c r="A38" s="21"/>
       <c r="B38" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.5">
       <c r="A39" s="21"/>
       <c r="B39" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16.5">
       <c r="A40" s="21"/>
       <c r="B40" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5">
       <c r="A41" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5">
       <c r="A42" s="21"/>
       <c r="B42" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16.5">
       <c r="A43" s="21"/>
       <c r="B43" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16.5">
       <c r="A44" s="21"/>
       <c r="B44" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5">
       <c r="A45" s="21"/>
       <c r="B45" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5">
       <c r="A46" s="21"/>
       <c r="B46" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5">
       <c r="A47" s="21"/>
       <c r="B47" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5">
       <c r="A48" s="21"/>
       <c r="B48" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5">
       <c r="A49" s="21"/>
       <c r="B49" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5">
       <c r="A50" s="21"/>
       <c r="B50" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5">
       <c r="A51" s="20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5">
       <c r="A52" s="21"/>
       <c r="B52" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5">
       <c r="A53" s="21"/>
       <c r="B53" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5">
       <c r="A54" s="21"/>
       <c r="B54" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5">
       <c r="A55" s="21"/>
       <c r="B55" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5">
       <c r="A56" s="21"/>
       <c r="B56" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16.5">
       <c r="A57" s="21"/>
       <c r="B57" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5">
       <c r="A58" s="21"/>
       <c r="B58" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="16.5">
       <c r="A59" s="21"/>
       <c r="B59" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16.5">
       <c r="A60" s="21"/>
       <c r="B60" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="16.5">
       <c r="A61" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="16.5">
       <c r="A62" s="21"/>
       <c r="B62" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="16.5">
       <c r="A63" s="21"/>
       <c r="B63" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="16.5">
       <c r="A64" s="21"/>
       <c r="B64" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="16.5">
       <c r="A65" s="21"/>
       <c r="B65" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="16.5">
       <c r="A66" s="21"/>
       <c r="B66" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="16.5">
       <c r="A67" s="21"/>
       <c r="B67" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="16.5">
       <c r="A68" s="21"/>
       <c r="B68" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="16.5">
       <c r="A69" s="21"/>
       <c r="B69" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="16.5">
       <c r="A70" s="21"/>
       <c r="B70" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16.5">
       <c r="A71" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="16.5">
       <c r="A72" s="21"/>
       <c r="B72" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="16.5">
       <c r="A73" s="21"/>
       <c r="B73" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="16.5">
       <c r="A74" s="21"/>
       <c r="B74" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16.5">
       <c r="A75" s="21"/>
       <c r="B75" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="16.5">
       <c r="A76" s="21"/>
       <c r="B76" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="16.5">
       <c r="A77" s="21"/>
       <c r="B77" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="16.5">
       <c r="A78" s="21"/>
       <c r="B78" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16.5">
       <c r="A79" s="21"/>
       <c r="B79" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="16.5">
       <c r="A80" s="21"/>
       <c r="B80" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="16.5">
       <c r="A81" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="16.5">
       <c r="A82" s="21"/>
       <c r="B82" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.5">
       <c r="A83" s="21"/>
       <c r="B83" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="16.5">
       <c r="A84" s="21"/>
       <c r="B84" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="16.5">
       <c r="A85" s="21"/>
       <c r="B85" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="16.5">
       <c r="A86" s="21"/>
       <c r="B86" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="16.5">
       <c r="A87" s="21"/>
       <c r="B87" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="16.5">
       <c r="A88" s="21"/>
       <c r="B88" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.5">
       <c r="A89" s="21"/>
       <c r="B89" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="16.5">
       <c r="A90" s="22"/>
       <c r="B90" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
